--- a/artfynd/A 53897-2025 artfynd.xlsx
+++ b/artfynd/A 53897-2025 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 53897-2025 artfynd.xlsx
+++ b/artfynd/A 53897-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98460405</v>
+        <v>98460908</v>
       </c>
       <c r="B2" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövliden, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576542.5697390328</v>
+        <v>576424</v>
       </c>
       <c r="R2" t="n">
-        <v>7171560.662635395</v>
+        <v>7171447</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,26 +744,16 @@
           <t>2022-02-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-02-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -792,51 +773,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98460908</v>
+        <v>101108053</v>
       </c>
       <c r="B3" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövliden, Ås lm</t>
+          <t>Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576423.9869085337</v>
+        <v>576616</v>
       </c>
       <c r="R3" t="n">
-        <v>7171447.078182728</v>
+        <v>7171748</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,29 +839,19 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-02-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-02-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -905,51 +871,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101107403</v>
+        <v>98460422</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövliden, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576532.5208655929</v>
+        <v>576454</v>
       </c>
       <c r="R4" t="n">
-        <v>7171652.561867795</v>
+        <v>7171471</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,22 +936,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-02-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2022-02-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,6 +975,118 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98460405</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lövliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>576543</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7171561</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-02-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-02-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Sara Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
